--- a/spider_telephone/电话号码判断9.xlsx
+++ b/spider_telephone/电话号码判断9.xlsx
@@ -432,481 +432,641 @@
       <c r="A2" t="n">
         <v>17620575867</v>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>17825055203</v>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>17825057929</v>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>17825065855</v>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>17825512210</v>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>17841381165</v>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>18028202086</v>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>18200640606</v>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>18200647882</v>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>18218034783</v>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>18218289839</v>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>18316599574</v>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>18316778830</v>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>18316831832</v>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>18319192636</v>
       </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>18319198491</v>
       </c>
-      <c r="B17" t="inlineStr"/>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>18319681583</v>
       </c>
-      <c r="B18" t="inlineStr"/>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>18319845482</v>
       </c>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>18319871110</v>
       </c>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>18575360150</v>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>18617227398</v>
       </c>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>18664041286</v>
       </c>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>18676281520</v>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>18681196588</v>
       </c>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>18819095550</v>
       </c>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>18819515476</v>
       </c>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>18819529542</v>
       </c>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>18819529607</v>
       </c>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>18819716894</v>
       </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>18820613120</v>
       </c>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>18824215560</v>
       </c>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>18824218525</v>
       </c>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>18824524452</v>
       </c>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>18824547819</v>
       </c>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>18824578908</v>
       </c>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
         <v>18825506001</v>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
         <v>18825506128</v>
       </c>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>18825562320</v>
       </c>
-      <c r="B39" t="inlineStr"/>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>18825566727</v>
       </c>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
         <v>18825755520</v>
       </c>
-      <c r="B41" t="inlineStr"/>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
         <v>18825763644</v>
       </c>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
         <v>18825786930</v>
       </c>
-      <c r="B43" t="inlineStr"/>
+      <c r="B43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
         <v>18825803885</v>
       </c>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>18825827943</v>
       </c>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>18825828363</v>
       </c>
-      <c r="B46" t="inlineStr"/>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
         <v>18825837564</v>
       </c>
-      <c r="B47" t="inlineStr"/>
+      <c r="B47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
         <v>18825842525</v>
       </c>
-      <c r="B48" t="inlineStr"/>
+      <c r="B48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>18825864934</v>
       </c>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
         <v>18826801936</v>
       </c>
-      <c r="B50" t="inlineStr"/>
+      <c r="B50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
         <v>18826810906</v>
       </c>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
         <v>18826812718</v>
       </c>
-      <c r="B52" t="inlineStr"/>
+      <c r="B52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
         <v>18826855849</v>
       </c>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
         <v>18826898824</v>
       </c>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
         <v>18826963812</v>
       </c>
-      <c r="B55" t="inlineStr"/>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
         <v>18826989491</v>
       </c>
-      <c r="B56" t="inlineStr"/>
+      <c r="B56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
         <v>18898711134</v>
       </c>
-      <c r="B57" t="inlineStr"/>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
         <v>18938585886</v>
       </c>
-      <c r="B58" t="inlineStr"/>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
         <v>19521709945</v>
       </c>
-      <c r="B59" t="inlineStr"/>
+      <c r="B59" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
         <v>19521801859</v>
       </c>
-      <c r="B60" t="inlineStr"/>
+      <c r="B60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
         <v>19521822784</v>
       </c>
-      <c r="B61" t="inlineStr"/>
+      <c r="B61" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
         <v>19521848757</v>
       </c>
-      <c r="B62" t="inlineStr"/>
+      <c r="B62" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
         <v>19521892648</v>
       </c>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
         <v>19525634214</v>
       </c>
-      <c r="B64" t="inlineStr"/>
+      <c r="B64" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
         <v>19525699969</v>
       </c>
-      <c r="B65" t="inlineStr"/>
+      <c r="B65" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
         <v>19525997136</v>
       </c>
-      <c r="B66" t="inlineStr"/>
+      <c r="B66" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
         <v>19525999742</v>
       </c>
-      <c r="B67" t="inlineStr"/>
+      <c r="B67" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
         <v>19525999843</v>
       </c>
-      <c r="B68" t="inlineStr"/>
+      <c r="B68" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
         <v>19526618584</v>
       </c>
-      <c r="B69" t="inlineStr"/>
+      <c r="B69" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
         <v>19526622692</v>
       </c>
-      <c r="B70" t="inlineStr"/>
+      <c r="B70" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
         <v>19526644381</v>
       </c>
-      <c r="B71" t="inlineStr"/>
+      <c r="B71" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
         <v>19536818705</v>
       </c>
-      <c r="B72" t="inlineStr"/>
+      <c r="B72" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
         <v>19536827258</v>
       </c>
-      <c r="B73" t="inlineStr"/>
+      <c r="B73" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
         <v>19537654643</v>
       </c>
-      <c r="B74" t="inlineStr"/>
+      <c r="B74" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
         <v>19537906358</v>
       </c>
-      <c r="B75" t="inlineStr"/>
+      <c r="B75" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
         <v>19539422752</v>
       </c>
-      <c r="B76" t="inlineStr"/>
+      <c r="B76" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
         <v>19820120190</v>
       </c>
-      <c r="B77" t="inlineStr"/>
+      <c r="B77" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
         <v>19865592304</v>
       </c>
-      <c r="B78" t="inlineStr"/>
+      <c r="B78" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
         <v>19876938366</v>
       </c>
-      <c r="B79" t="inlineStr"/>
+      <c r="B79" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
         <v>19876969212</v>
       </c>
-      <c r="B80" t="inlineStr"/>
+      <c r="B80" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
         <v>19878970549</v>
       </c>
-      <c r="B81" t="inlineStr"/>
+      <c r="B81" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/spider_telephone/电话号码判断9.xlsx
+++ b/spider_telephone/电话号码判断9.xlsx
@@ -505,567 +505,707 @@
         <v>18218034783</v>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>18218289839</v>
       </c>
-      <c r="B12" t="n">
-        <v>1</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>18316599574</v>
       </c>
-      <c r="B13" t="n">
-        <v>0</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>18316778830</v>
       </c>
-      <c r="B14" t="n">
-        <v>0</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>18316831832</v>
       </c>
-      <c r="B15" t="n">
-        <v>1</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>18319192636</v>
       </c>
-      <c r="B16" t="n">
-        <v>0</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>18319198491</v>
       </c>
-      <c r="B17" t="n">
-        <v>0</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>18319681583</v>
       </c>
-      <c r="B18" t="n">
-        <v>0</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>18319845482</v>
       </c>
-      <c r="B19" t="n">
-        <v>1</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>18319871110</v>
       </c>
-      <c r="B20" t="n">
-        <v>1</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>18575360150</v>
       </c>
-      <c r="B21" t="n">
-        <v>1</v>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>18617227398</v>
       </c>
-      <c r="B22" t="n">
-        <v>1</v>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>18664041286</v>
       </c>
-      <c r="B23" t="n">
-        <v>1</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>18676281520</v>
       </c>
-      <c r="B24" t="n">
-        <v>1</v>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>18681196588</v>
       </c>
-      <c r="B25" t="n">
-        <v>1</v>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>18819095550</v>
       </c>
-      <c r="B26" t="n">
-        <v>1</v>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>18819515476</v>
       </c>
-      <c r="B27" t="n">
-        <v>1</v>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>18819529542</v>
       </c>
-      <c r="B28" t="n">
-        <v>1</v>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>18819529607</v>
       </c>
-      <c r="B29" t="n">
-        <v>1</v>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>18819716894</v>
       </c>
-      <c r="B30" t="n">
-        <v>1</v>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>18820613120</v>
       </c>
-      <c r="B31" t="n">
-        <v>1</v>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>18824215560</v>
       </c>
-      <c r="B32" t="n">
-        <v>0</v>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>18824218525</v>
       </c>
-      <c r="B33" t="n">
-        <v>0</v>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>18824524452</v>
       </c>
-      <c r="B34" t="n">
-        <v>0</v>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>18824547819</v>
       </c>
-      <c r="B35" t="n">
-        <v>1</v>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>18824578908</v>
       </c>
-      <c r="B36" t="n">
-        <v>0</v>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
         <v>18825506001</v>
       </c>
-      <c r="B37" t="n">
-        <v>0</v>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
         <v>18825506128</v>
       </c>
-      <c r="B38" t="n">
-        <v>0</v>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>18825562320</v>
       </c>
-      <c r="B39" t="n">
-        <v>0</v>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>18825566727</v>
       </c>
-      <c r="B40" t="n">
-        <v>1</v>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
         <v>18825755520</v>
       </c>
-      <c r="B41" t="n">
-        <v>0</v>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
         <v>18825763644</v>
       </c>
-      <c r="B42" t="n">
-        <v>0</v>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
         <v>18825786930</v>
       </c>
-      <c r="B43" t="n">
-        <v>0</v>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
         <v>18825803885</v>
       </c>
-      <c r="B44" t="n">
-        <v>0</v>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>18825827943</v>
       </c>
-      <c r="B45" t="n">
-        <v>1</v>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>18825828363</v>
       </c>
-      <c r="B46" t="n">
-        <v>1</v>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
         <v>18825837564</v>
       </c>
-      <c r="B47" t="n">
-        <v>0</v>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
         <v>18825842525</v>
       </c>
-      <c r="B48" t="n">
-        <v>0</v>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>18825864934</v>
       </c>
-      <c r="B49" t="n">
-        <v>0</v>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
         <v>18826801936</v>
       </c>
-      <c r="B50" t="n">
-        <v>0</v>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
         <v>18826810906</v>
       </c>
-      <c r="B51" t="n">
-        <v>0</v>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
         <v>18826812718</v>
       </c>
-      <c r="B52" t="n">
-        <v>0</v>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
         <v>18826855849</v>
       </c>
-      <c r="B53" t="n">
-        <v>1</v>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
         <v>18826898824</v>
       </c>
-      <c r="B54" t="n">
-        <v>0</v>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
         <v>18826963812</v>
       </c>
-      <c r="B55" t="n">
-        <v>1</v>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
         <v>18826989491</v>
       </c>
-      <c r="B56" t="n">
-        <v>0</v>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
         <v>18898711134</v>
       </c>
-      <c r="B57" t="n">
-        <v>1</v>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
         <v>18938585886</v>
       </c>
-      <c r="B58" t="n">
-        <v>1</v>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
         <v>19521709945</v>
       </c>
-      <c r="B59" t="n">
-        <v>0</v>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
         <v>19521801859</v>
       </c>
-      <c r="B60" t="n">
-        <v>0</v>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
         <v>19521822784</v>
       </c>
-      <c r="B61" t="n">
-        <v>1</v>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
         <v>19521848757</v>
       </c>
-      <c r="B62" t="n">
-        <v>0</v>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
         <v>19521892648</v>
       </c>
-      <c r="B63" t="n">
-        <v>0</v>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
         <v>19525634214</v>
       </c>
-      <c r="B64" t="n">
-        <v>0</v>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
         <v>19525699969</v>
       </c>
-      <c r="B65" t="n">
-        <v>0</v>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
         <v>19525997136</v>
       </c>
-      <c r="B66" t="n">
-        <v>0</v>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
         <v>19525999742</v>
       </c>
-      <c r="B67" t="n">
-        <v>0</v>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
         <v>19525999843</v>
       </c>
-      <c r="B68" t="n">
-        <v>0</v>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
         <v>19526618584</v>
       </c>
-      <c r="B69" t="n">
-        <v>0</v>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
         <v>19526622692</v>
       </c>
-      <c r="B70" t="n">
-        <v>0</v>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
         <v>19526644381</v>
       </c>
-      <c r="B71" t="n">
-        <v>0</v>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
         <v>19536818705</v>
       </c>
-      <c r="B72" t="n">
-        <v>0</v>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
         <v>19536827258</v>
       </c>
-      <c r="B73" t="n">
-        <v>0</v>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
         <v>19537654643</v>
       </c>
-      <c r="B74" t="n">
-        <v>0</v>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
         <v>19537906358</v>
       </c>
-      <c r="B75" t="n">
-        <v>0</v>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
         <v>19539422752</v>
       </c>
-      <c r="B76" t="n">
-        <v>0</v>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
         <v>19820120190</v>
       </c>
-      <c r="B77" t="n">
-        <v>0</v>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
         <v>19865592304</v>
       </c>
-      <c r="B78" t="n">
-        <v>0</v>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
         <v>19876938366</v>
       </c>
-      <c r="B79" t="n">
-        <v>0</v>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
         <v>19876969212</v>
       </c>
-      <c r="B80" t="n">
-        <v>0</v>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
         <v>19878970549</v>
       </c>
-      <c r="B81" t="n">
-        <v>0</v>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
   </sheetData>
